--- a/题库/PY程序设计实验-模拟题2.xlsx
+++ b/题库/PY程序设计实验-模拟题2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="11950" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,51 +62,57 @@
     <t>Prog2.1.py</t>
   </si>
   <si>
-    <t>def IsPrime(n):
-    flag = 0
-    for i in range(2, n):
+    <t xml:space="preserve">    for i in range(2, n):
         if n % i == 0:
-            flag = 1
-            return flag
+            flag = 1           
     return flag</t>
   </si>
   <si>
     <t>Prog2.2.py</t>
   </si>
   <si>
-    <t>def fun(m,n):
-    if m &lt; n:
-        m, n = n, m
-    p = m * n
+    <t>if m &lt; n:
+    m, n = n, m
+p = m * n
+r = m % n
+while r != 0:
+    m = n
+    n = r
     r = m % n
-    while r != 0:
-        m, n = n, r
-        r = m % n
-    return (int(p/n), n)</t>
-  </si>
-  <si>
-    <t>Prog2.3py</t>
-  </si>
-  <si>
-    <t>n = int(input("请输入一个整数："))
-s = 0
+return (int(p / n), n)</t>
+  </si>
+  <si>
+    <t>Prog2.3.py</t>
+  </si>
+  <si>
+    <t>s = 0
+n = int(input("请输入一个整数："))
 for i in range(1, n+1):
     s = s + i
 print(s)</t>
   </si>
   <si>
-    <t>Prog2.4py</t>
-  </si>
-  <si>
-    <t>s = 0
-t = 100
-while t &lt;= 200:
-    s = s + t
-    t = t + 1
+    <t>Prog2.4.py</t>
+  </si>
+  <si>
+    <t>s=0
+t=100
+while 1:
+    s=s+t
+    t=t+1
+    if t&gt;200:
+        break
+print("100到200和是{}".format(s))
+--------------------------------------------------
+s=0
+t=100
+while (t&lt;200):
+    t=t+1
+    s=s+t
 print("100到200和是{}".format(s))</t>
   </si>
   <si>
-    <t>Prog2.5py</t>
+    <t>Prog2.5.py</t>
   </si>
   <si>
     <t>s = 0
@@ -115,7 +121,7 @@
 print("1到50和是{}".format(s))</t>
   </si>
   <si>
-    <t>Prog2.6py</t>
+    <t>Prog2.6.py</t>
   </si>
   <si>
     <t>x = int(input("请输入第一个整数："))
@@ -129,7 +135,7 @@
     print("符号输入错误")</t>
   </si>
   <si>
-    <t>Prog2.7py</t>
+    <t>Prog2.7.py</t>
   </si>
   <si>
     <t>a = int(input("请输入第一条边："))
@@ -141,17 +147,17 @@
     print(a, b, c, "不可以构成一个三角形")</t>
   </si>
   <si>
-    <t>Prog2.8py</t>
-  </si>
-  <si>
-    <t>n = int(input("请输入一个整数："))
-if n % 2 == 0:
-    print(n, "是偶数")
+    <t>Prog2.8.py</t>
+  </si>
+  <si>
+    <t>n=int(input("【请输入一个整数：】 "))
+if n%2==0:
+    print("{}是偶数".format(n))
 else:
-    print(n, "是奇数")</t>
-  </si>
-  <si>
-    <t>Prog2.9py</t>
+    print("{}是奇数".format(n))</t>
+  </si>
+  <si>
+    <t>Prog2.9.py</t>
   </si>
   <si>
     <t>name = input("【请输入姓名：】")
@@ -162,7 +168,7 @@
     print(name, "不合格")</t>
   </si>
   <si>
-    <t>Prog2.10py</t>
+    <t>Prog2.10.py</t>
   </si>
   <si>
     <t>year = int(input("【请输入年份：】"))
@@ -681,175 +687,173 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1165,230 +1169,230 @@
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="6" width="23.1818181818182" customWidth="1"/>
+    <col min="1" max="6" width="23.1818181818182" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="76" customHeight="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" ht="76" customHeight="1" spans="1:9">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>10</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="I2" s="7" t="s">
+      <c r="G2" s="6"/>
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="76" customHeight="1" spans="1:6">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" spans="1:6">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" spans="1:6">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" spans="1:6">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" spans="1:6">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" spans="1:6">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" spans="1:6">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1" spans="1:6">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1" spans="1:6">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>10</v>
       </c>
     </row>
